--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.82076143433934</v>
+        <v>8.745873733080144</v>
       </c>
       <c r="D2" t="n">
-        <v>55.08673516882055</v>
+        <v>8.95159446493334</v>
       </c>
       <c r="E2" t="n">
-        <v>12.76963870763831</v>
+        <v>2.075066289991225</v>
       </c>
       <c r="F2" t="n">
-        <v>13.13253159557522</v>
+        <v>2.134036384280974</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.97596239411759</v>
+        <v>7.633593889044108</v>
       </c>
       <c r="D3" t="n">
-        <v>47.95576178075196</v>
+        <v>7.792811289372194</v>
       </c>
       <c r="E3" t="n">
-        <v>12.76963870763831</v>
+        <v>2.075066289991225</v>
       </c>
       <c r="F3" t="n">
-        <v>13.13253159557522</v>
+        <v>2.134036384280974</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.21602904470871</v>
+        <v>6.697604719765166</v>
       </c>
       <c r="D4" t="n">
-        <v>41.99647181073563</v>
+        <v>6.82442666924454</v>
       </c>
       <c r="E4" t="n">
-        <v>12.76963870763831</v>
+        <v>2.075066289991225</v>
       </c>
       <c r="F4" t="n">
-        <v>13.13253159557522</v>
+        <v>2.134036384280974</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.58649366589846</v>
+        <v>6.107805220708499</v>
       </c>
       <c r="D5" t="n">
-        <v>38.7979469185012</v>
+        <v>6.304666374256445</v>
       </c>
       <c r="E5" t="n">
-        <v>12.76963870763831</v>
+        <v>2.075066289991225</v>
       </c>
       <c r="F5" t="n">
-        <v>13.13253159557522</v>
+        <v>2.134036384280974</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.54729091761639</v>
+        <v>5.938934774112664</v>
       </c>
       <c r="D6" t="n">
-        <v>37.69070652870145</v>
+        <v>6.124739810913987</v>
       </c>
       <c r="E6" t="n">
-        <v>12.76963870763831</v>
+        <v>2.075066289991225</v>
       </c>
       <c r="F6" t="n">
-        <v>13.13253159557522</v>
+        <v>2.134036384280974</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.44314938910409</v>
+        <v>3.647011775729414</v>
       </c>
       <c r="D7" t="n">
-        <v>23.10550086962553</v>
+        <v>3.754643891314149</v>
       </c>
       <c r="E7" t="n">
-        <v>12.76963870763831</v>
+        <v>2.075066289991225</v>
       </c>
       <c r="F7" t="n">
-        <v>13.13253159557522</v>
+        <v>2.134036384280974</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.89768537983023</v>
+        <v>2.745873874222413</v>
       </c>
       <c r="D8" t="n">
-        <v>16.19773829179953</v>
+        <v>2.632132472417425</v>
       </c>
       <c r="E8" t="n">
-        <v>12.76963870763831</v>
+        <v>2.075066289991225</v>
       </c>
       <c r="F8" t="n">
-        <v>13.13253159557522</v>
+        <v>2.134036384280974</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.68721681442228</v>
+        <v>8.886672732343621</v>
       </c>
       <c r="D9" t="n">
-        <v>55.10408926955592</v>
+        <v>8.954414506302838</v>
       </c>
       <c r="E9" t="n">
-        <v>12.76963870763831</v>
+        <v>2.075066289991225</v>
       </c>
       <c r="F9" t="n">
-        <v>13.13253159557522</v>
+        <v>2.134036384280974</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
